--- a/data/xizi_card_1.xlsx
+++ b/data/xizi_card_1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12960" activeTab="1"/>
+    <workbookView windowWidth="25600" windowHeight="12790"/>
   </bookViews>
   <sheets>
     <sheet name="首页及工序页" sheetId="1" r:id="rId1"/>
@@ -14,23 +14,23 @@
     <sheet name="更改记录页" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">首页及工序页!$28:$30</definedName>
-    <definedName name="会签1">首页及工序页!$K$25</definedName>
-    <definedName name="会签1时间">首页及工序页!$K$26</definedName>
-    <definedName name="会签2">首页及工序页!$L$25</definedName>
-    <definedName name="会签2时间">首页及工序页!$L$26</definedName>
-    <definedName name="会签3">首页及工序页!$M$25</definedName>
-    <definedName name="会签3时间">首页及工序页!$M$26</definedName>
-    <definedName name="会签4">首页及工序页!$N$25</definedName>
-    <definedName name="会签4时间">首页及工序页!$N$26</definedName>
-    <definedName name="批准">首页及工序页!$F$25</definedName>
-    <definedName name="批准时间">首页及工序页!$F$26</definedName>
-    <definedName name="设计">首页及工序页!$A$25</definedName>
-    <definedName name="设计时间">首页及工序页!$A$26</definedName>
-    <definedName name="校对">首页及工序页!$C$25</definedName>
-    <definedName name="校对时间">首页及工序页!$C$26</definedName>
-    <definedName name="质保">首页及工序页!$D$25</definedName>
-    <definedName name="质保时间">首页及工序页!$D$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">首页及工序页!$1:$3</definedName>
+    <definedName name="会签1">首页及工序页!#REF!</definedName>
+    <definedName name="会签1时间">首页及工序页!#REF!</definedName>
+    <definedName name="会签2">首页及工序页!#REF!</definedName>
+    <definedName name="会签2时间">首页及工序页!#REF!</definedName>
+    <definedName name="会签3">首页及工序页!#REF!</definedName>
+    <definedName name="会签3时间">首页及工序页!#REF!</definedName>
+    <definedName name="会签4">首页及工序页!#REF!</definedName>
+    <definedName name="会签4时间">首页及工序页!#REF!</definedName>
+    <definedName name="批准">首页及工序页!#REF!</definedName>
+    <definedName name="批准时间">首页及工序页!#REF!</definedName>
+    <definedName name="设计">首页及工序页!#REF!</definedName>
+    <definedName name="设计时间">首页及工序页!#REF!</definedName>
+    <definedName name="校对">首页及工序页!#REF!</definedName>
+    <definedName name="校对时间">首页及工序页!#REF!</definedName>
+    <definedName name="质保">首页及工序页!#REF!</definedName>
+    <definedName name="质保时间">首页及工序页!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +50,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="110">
+  <si>
+    <t>XXX</t>
+  </si>
   <si>
     <t>制造流程卡
 Fabrication  Traveler</t>
@@ -112,1044 +115,6 @@
   </si>
   <si>
     <t>A4</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">客户
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Customer</t>
-    </r>
-  </si>
-  <si>
-    <t>Stelia</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">项目号
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Program No.</t>
-    </r>
-  </si>
-  <si>
-    <t>SA0002</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">有效架次
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Effective S/S</t>
-    </r>
-  </si>
-  <si>
-    <t>XZA10194+</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7.5"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">是否关重件
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7.5"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Key/IMPT Part</t>
-    </r>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">生产计划员
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Production Planner</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">零件号
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Part No.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">零件名称
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Part Name</t>
-    </r>
-  </si>
-  <si>
-    <t>CLEAT ST22-25 FR29</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">零件版次
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Part issue</t>
-    </r>
-  </si>
-  <si>
-    <t>A00</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">产品系列号
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Ser. No.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>分卡信息</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> SPLIT INFORMATION</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">分卡日期
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>DATE</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">工序号
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>O.P. No.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">分卡数量
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>SPLIT QTY</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>产品系列号</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>若有</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)
-SER No.(if any)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">结余数量
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>BALANCE</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">去向
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>TO</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">来源
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>FROM</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">分卡者
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>SPLIT BY</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">检验
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>INSPECTOR</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>所引用的图纸及技术资料</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> Related drawings and technical files</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">序号
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Serial No.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>编号</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 
-Number</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">名称
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Name</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">页次
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Page</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">版次
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Issue</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">备注
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Note</t>
-    </r>
-  </si>
-  <si>
-    <t>E53234023</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>图纸</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>DWG</t>
-    </r>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>01-03</t>
-  </si>
-  <si>
-    <t>AMPR_E53234023200-01</t>
-  </si>
-  <si>
-    <t>AMPR</t>
-  </si>
-  <si>
-    <t>00</t>
-  </si>
-  <si>
-    <t>NLGB-TQN-0210</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>询问单</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>query</t>
-    </r>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>CDF-TQN-0260</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>所需原材料信息</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> MATERIAL REQUIRED</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">材料名称
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>MAT'L NAME</t>
-    </r>
-  </si>
-  <si>
-    <t>铝薄板</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>材料牌号状态</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 
-MAT'L DESP' S</t>
-    </r>
-  </si>
-  <si>
-    <t>2024-O</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>材料规格</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 
-MAT'L SIZE(mm/inch)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">材料编码
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>MAT'L CODE</t>
-    </r>
-  </si>
-  <si>
-    <t>XAZ51C00032-22</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="7.5"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">纤维方向
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="7.5"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>GRAIN DIRECTION</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">毛料尺寸
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>STOCK SIZE</t>
-    </r>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>做</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>材料规范</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 
-MAT'L SPEC</t>
-    </r>
-  </si>
-  <si>
-    <t>ASNA3042</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">炉批号
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>LOT No.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">发料者
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Released By</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>工作说明</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> JOB DESCRIPTION</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">编制
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>COMPILED BY</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">校对
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>CHECKED BY.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">质保
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Q</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>．</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>A</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">批准
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>APPROVED BY</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">会签
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> COUNTERSIGNED BY</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">归档人员
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Archivist</t>
-    </r>
   </si>
   <si>
     <r>
@@ -3507,6 +2472,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>说明</t>
     </r>
     <r>
@@ -3617,25 +2587,6 @@
       </rPr>
       <t>2
 Sketch 2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>说明</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve">
-Note</t>
     </r>
   </si>
   <si>
@@ -4220,7 +3171,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="66">
+  <fonts count="49">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4296,18 +3247,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
@@ -4331,20 +3270,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4369,46 +3296,6 @@
       <b/>
       <sz val="8"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="7.5"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="7.5"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8.8"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
@@ -4573,12 +3460,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8"/>
+      <sz val="8.8"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -4589,25 +3471,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="8.8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="7.5"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -4622,16 +3487,6 @@
       <sz val="8.8"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="7.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -4840,7 +3695,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -4979,26 +3834,6 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -5115,143 +3950,143 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="4" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="5" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="6" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="41" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="40" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5309,9 +4144,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -5321,7 +4153,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="50">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="50">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5354,25 +4186,25 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="50" applyFont="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="50" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5399,28 +4231,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5429,10 +4255,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5444,239 +4270,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="13" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="9" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="11" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="10" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="11" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5743,89 +4367,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>53534</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>36399</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="890516" cy="552042"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图形 1"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="434340" y="36195"/>
-          <a:ext cx="890270" cy="551815"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>53534</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>36399</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="890516" cy="552042"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图形 2"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="434340" y="6553200"/>
-          <a:ext cx="890270" cy="551815"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -5900,8 +4441,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2120265" y="1381125"/>
-          <a:ext cx="7266940" cy="3698875"/>
+          <a:off x="1971675" y="1381125"/>
+          <a:ext cx="6743065" cy="3698875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5913,7 +4454,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -5988,8 +4529,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3474085" y="1492250"/>
-          <a:ext cx="4216400" cy="3419475"/>
+          <a:off x="3251200" y="1492250"/>
+          <a:ext cx="3834765" cy="3419475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6001,7 +4542,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -6045,7 +4586,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -6376,40 +4917,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Z47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:Z20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="13.0916666666667" customWidth="1"/>
-    <col min="4" max="4" width="11.725" customWidth="1"/>
-    <col min="5" max="5" width="5.45" customWidth="1"/>
-    <col min="6" max="6" width="3.45" customWidth="1"/>
-    <col min="7" max="7" width="4.63333333333333" customWidth="1"/>
-    <col min="8" max="8" width="4.26666666666667" customWidth="1"/>
-    <col min="9" max="9" width="3.45" customWidth="1"/>
-    <col min="10" max="10" width="2.45" customWidth="1"/>
-    <col min="11" max="11" width="11.725" customWidth="1"/>
-    <col min="12" max="12" width="11.3666666666667" customWidth="1"/>
-    <col min="13" max="13" width="14.0916666666667" customWidth="1"/>
-    <col min="14" max="14" width="2.725" customWidth="1"/>
+    <col min="3" max="3" width="13.0909090909091" customWidth="1"/>
+    <col min="4" max="4" width="11.7272727272727" customWidth="1"/>
+    <col min="5" max="5" width="5.44545454545455" customWidth="1"/>
+    <col min="6" max="6" width="3.45454545454545" customWidth="1"/>
+    <col min="7" max="7" width="4.63636363636364" customWidth="1"/>
+    <col min="8" max="8" width="4.26363636363636" customWidth="1"/>
+    <col min="9" max="9" width="3.45454545454545" customWidth="1"/>
+    <col min="10" max="10" width="2.45454545454545" customWidth="1"/>
+    <col min="11" max="11" width="11.7272727272727" customWidth="1"/>
+    <col min="12" max="12" width="11.3636363636364" customWidth="1"/>
+    <col min="13" max="13" width="14.0909090909091" customWidth="1"/>
+    <col min="14" max="14" width="2.72727272727273" customWidth="1"/>
     <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="0.908333333333333" customWidth="1"/>
-    <col min="17" max="17" width="5.09166666666667" customWidth="1"/>
-    <col min="18" max="18" width="0.908333333333333" customWidth="1"/>
-    <col min="19" max="19" width="8.36666666666667" customWidth="1"/>
-    <col min="20" max="20" width="14.45" customWidth="1"/>
+    <col min="16" max="16" width="0.909090909090909" customWidth="1"/>
+    <col min="17" max="17" width="5.09090909090909" customWidth="1"/>
+    <col min="18" max="18" width="0.909090909090909" customWidth="1"/>
+    <col min="19" max="19" width="8.36363636363636" customWidth="1"/>
+    <col min="20" max="20" width="14.4454545454545" customWidth="1"/>
     <col min="22" max="25" width="9" hidden="1" customWidth="1"/>
-    <col min="26" max="26" width="58.725" hidden="1" customWidth="1"/>
+    <col min="26" max="26" width="58.7272727272727" hidden="1" customWidth="1"/>
     <col min="27" max="29" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:20">
-      <c r="A1" s="2"/>
-      <c r="B1" s="57"/>
-      <c r="C1" s="58"/>
+    <row r="1" ht="25" customHeight="1" spans="1:26">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="55"/>
       <c r="D1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -6419,23 +4962,23 @@
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
-      <c r="M1" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="59" t="s">
+      <c r="M1" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="59"/>
-      <c r="T1" s="59"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57"/>
+      <c r="Q1" s="57"/>
+      <c r="R1" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
     </row>
-    <row r="2" ht="25" customHeight="1" spans="1:20">
-      <c r="A2" s="61"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="63"/>
+    <row r="2" ht="25" customHeight="1" spans="1:26">
+      <c r="A2" s="58"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="60"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -6445,1148 +4988,350 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="64" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="65" t="s">
+      <c r="M2" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="65"/>
-      <c r="P2" s="66" t="s">
+      <c r="N2" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="67" t="s">
+      <c r="O2" s="62"/>
+      <c r="P2" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="R2" s="68"/>
-      <c r="S2" s="69"/>
-      <c r="T2" s="69"/>
+      <c r="Q2" s="64" t="s">
+        <v>7</v>
+      </c>
+      <c r="R2" s="65"/>
+      <c r="S2" s="66"/>
+      <c r="T2" s="66"/>
     </row>
-    <row r="3" s="55" customFormat="1" ht="21" customHeight="1" spans="1:20">
-      <c r="A3" s="70" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="71" t="s">
+    <row r="3" s="1" customFormat="1" ht="24" customHeight="1" spans="1:26">
+      <c r="A3" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="70" t="s">
+      <c r="B3" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="72" t="s">
+      <c r="C3" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="74"/>
-      <c r="I3" s="75" t="s">
+      <c r="D3" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="76"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="78" t="s">
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="79" t="s">
+      <c r="N3" s="67"/>
+      <c r="O3" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="72" t="s">
+      <c r="P3" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73"/>
-      <c r="Q3" s="74"/>
-      <c r="R3" s="80" t="s">
-        <v>15</v>
-      </c>
-      <c r="S3" s="81"/>
-      <c r="T3" s="82"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
     </row>
-    <row r="4" s="55" customFormat="1" ht="26.25" customHeight="1" spans="1:20">
-      <c r="A4" s="70" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="70"/>
-      <c r="C4" s="78" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="70" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="75" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="76"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="78" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="70" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="72" t="str">
-        <f>IF(N3="否","N/A","")</f>
-        <v>N/A</v>
-      </c>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="74"/>
-      <c r="R4" s="80"/>
-      <c r="S4" s="81"/>
-      <c r="T4" s="82"/>
-    </row>
-    <row r="5" s="55" customFormat="1" ht="15" spans="1:20">
-      <c r="A5" s="83" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="85"/>
-    </row>
-    <row r="6" s="55" customFormat="1" ht="21" spans="1:20">
-      <c r="A6" s="70" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="70"/>
-      <c r="C6" s="70" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="70" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="70"/>
-      <c r="F6" s="70" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="70"/>
-      <c r="H6" s="70"/>
-      <c r="I6" s="70"/>
-      <c r="J6" s="70"/>
-      <c r="K6" s="70"/>
-      <c r="L6" s="70" t="s">
-        <v>27</v>
-      </c>
-      <c r="M6" s="70" t="s">
-        <v>28</v>
-      </c>
-      <c r="N6" s="70" t="s">
-        <v>29</v>
-      </c>
-      <c r="O6" s="70"/>
-      <c r="P6" s="70"/>
-      <c r="Q6" s="70"/>
-      <c r="R6" s="70" t="s">
-        <v>30</v>
-      </c>
-      <c r="S6" s="70"/>
-      <c r="T6" s="70" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" s="55" customFormat="1" ht="21" customHeight="1" spans="1:20">
-      <c r="A7" s="72"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="74"/>
-      <c r="L7" s="86"/>
-      <c r="M7" s="86"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="73"/>
-      <c r="P7" s="73"/>
-      <c r="Q7" s="74"/>
-      <c r="R7" s="72"/>
-      <c r="S7" s="74"/>
-      <c r="T7" s="78"/>
-    </row>
-    <row r="8" s="55" customFormat="1" ht="21" customHeight="1" spans="1:20">
-      <c r="A8" s="72"/>
-      <c r="B8" s="74"/>
-      <c r="C8" s="78"/>
-      <c r="D8" s="72"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="73"/>
-      <c r="K8" s="74"/>
-      <c r="L8" s="86"/>
-      <c r="M8" s="86"/>
-      <c r="N8" s="72"/>
-      <c r="O8" s="73"/>
-      <c r="P8" s="73"/>
-      <c r="Q8" s="74"/>
-      <c r="R8" s="72"/>
-      <c r="S8" s="74"/>
-      <c r="T8" s="78"/>
-    </row>
-    <row r="9" s="55" customFormat="1" ht="21" customHeight="1" spans="1:20">
-      <c r="A9" s="72"/>
-      <c r="B9" s="74"/>
-      <c r="C9" s="78"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="73"/>
-      <c r="K9" s="74"/>
-      <c r="L9" s="86"/>
-      <c r="M9" s="86"/>
-      <c r="N9" s="72"/>
-      <c r="O9" s="73"/>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="74"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="74"/>
-      <c r="T9" s="78"/>
-    </row>
-    <row r="10" s="55" customFormat="1" ht="15" spans="1:20">
-      <c r="A10" s="87" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="88"/>
-      <c r="C10" s="88"/>
-      <c r="D10" s="88"/>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="88"/>
-      <c r="I10" s="88"/>
-      <c r="J10" s="88"/>
-      <c r="K10" s="88"/>
-      <c r="L10" s="88"/>
-      <c r="M10" s="88"/>
-      <c r="N10" s="88"/>
-      <c r="O10" s="88"/>
-      <c r="P10" s="88"/>
-      <c r="Q10" s="88"/>
-      <c r="R10" s="88"/>
-      <c r="S10" s="88"/>
-      <c r="T10" s="89"/>
-    </row>
-    <row r="11" s="55" customFormat="1" ht="21" spans="1:20">
-      <c r="A11" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="90"/>
-      <c r="E11" s="90"/>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="90"/>
-      <c r="J11" s="90"/>
-      <c r="K11" s="70" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="90"/>
-      <c r="M11" s="70" t="s">
-        <v>36</v>
-      </c>
-      <c r="N11" s="75" t="s">
-        <v>37</v>
-      </c>
-      <c r="O11" s="76"/>
-      <c r="P11" s="76"/>
-      <c r="Q11" s="77"/>
-      <c r="R11" s="75" t="s">
-        <v>38</v>
-      </c>
-      <c r="S11" s="76"/>
-      <c r="T11" s="77"/>
-    </row>
-    <row r="12" s="55" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A12" s="72">
-        <v>1</v>
-      </c>
-      <c r="B12" s="74"/>
-      <c r="C12" s="72" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="73"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="72" t="s">
-        <v>40</v>
-      </c>
-      <c r="L12" s="74"/>
-      <c r="M12" s="91" t="s">
-        <v>41</v>
-      </c>
-      <c r="N12" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="O12" s="93"/>
-      <c r="P12" s="93"/>
-      <c r="Q12" s="94"/>
-      <c r="R12" s="72" t="s">
-        <v>5</v>
-      </c>
-      <c r="S12" s="73"/>
-      <c r="T12" s="74"/>
-    </row>
-    <row r="13" s="55" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A13" s="72">
-        <v>2</v>
-      </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="72" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="L13" s="74"/>
-      <c r="M13" s="91" t="s">
-        <v>43</v>
-      </c>
-      <c r="N13" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="O13" s="93"/>
-      <c r="P13" s="93"/>
-      <c r="Q13" s="94"/>
-      <c r="R13" s="72" t="s">
-        <v>5</v>
-      </c>
-      <c r="S13" s="73"/>
-      <c r="T13" s="74"/>
-    </row>
-    <row r="14" s="55" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A14" s="72">
-        <v>3</v>
-      </c>
-      <c r="B14" s="74"/>
-      <c r="C14" s="72" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="74"/>
-      <c r="K14" s="72" t="s">
-        <v>45</v>
-      </c>
-      <c r="L14" s="74"/>
-      <c r="M14" s="91" t="s">
-        <v>41</v>
-      </c>
-      <c r="N14" s="92" t="s">
-        <v>46</v>
-      </c>
-      <c r="O14" s="93"/>
-      <c r="P14" s="93"/>
-      <c r="Q14" s="94"/>
-      <c r="R14" s="72" t="s">
-        <v>5</v>
-      </c>
-      <c r="S14" s="73"/>
-      <c r="T14" s="74"/>
-    </row>
-    <row r="15" s="55" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A15" s="72">
-        <v>4</v>
-      </c>
-      <c r="B15" s="74"/>
-      <c r="C15" s="72" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="73"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="74"/>
-      <c r="K15" s="72" t="s">
-        <v>48</v>
-      </c>
-      <c r="L15" s="74"/>
-      <c r="M15" s="91" t="s">
-        <v>41</v>
-      </c>
-      <c r="N15" s="92" t="s">
-        <v>49</v>
-      </c>
-      <c r="O15" s="93"/>
-      <c r="P15" s="93"/>
-      <c r="Q15" s="94"/>
-      <c r="R15" s="72" t="s">
-        <v>5</v>
-      </c>
-      <c r="S15" s="73"/>
-      <c r="T15" s="74"/>
-    </row>
-    <row r="16" s="55" customFormat="1" ht="15" customHeight="1" spans="1:20">
-      <c r="A16" s="72">
-        <v>5</v>
-      </c>
-      <c r="B16" s="74"/>
-      <c r="C16" s="72" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="73"/>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="73"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="72" t="s">
-        <v>48</v>
-      </c>
-      <c r="L16" s="74"/>
-      <c r="M16" s="91" t="s">
-        <v>41</v>
-      </c>
-      <c r="N16" s="92" t="s">
-        <v>49</v>
-      </c>
-      <c r="O16" s="93"/>
-      <c r="P16" s="93"/>
-      <c r="Q16" s="94"/>
-      <c r="R16" s="72" t="s">
-        <v>5</v>
-      </c>
-      <c r="S16" s="73"/>
-      <c r="T16" s="74"/>
-    </row>
-    <row r="17" s="55" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A17" s="72"/>
-      <c r="B17" s="74"/>
-      <c r="C17" s="72"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="73"/>
-      <c r="J17" s="74"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="74"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="92"/>
-      <c r="O17" s="93"/>
-      <c r="P17" s="93"/>
-      <c r="Q17" s="94"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="73"/>
-      <c r="T17" s="74"/>
-    </row>
-    <row r="18" s="55" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A18" s="72"/>
-      <c r="B18" s="74"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="73"/>
-      <c r="J18" s="74"/>
-      <c r="K18" s="72"/>
-      <c r="L18" s="74"/>
-      <c r="M18" s="91"/>
-      <c r="N18" s="92"/>
-      <c r="O18" s="93"/>
-      <c r="P18" s="93"/>
-      <c r="Q18" s="94"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="73"/>
-      <c r="T18" s="74"/>
-    </row>
-    <row r="19" s="55" customFormat="1" ht="15" customHeight="1" spans="1:26">
-      <c r="A19" s="87" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="88"/>
-      <c r="E19" s="88"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="88"/>
-      <c r="I19" s="88"/>
-      <c r="J19" s="88"/>
-      <c r="K19" s="88"/>
-      <c r="L19" s="88"/>
-      <c r="M19" s="88"/>
-      <c r="N19" s="88"/>
-      <c r="O19" s="88"/>
-      <c r="P19" s="88"/>
-      <c r="Q19" s="88"/>
-      <c r="R19" s="88"/>
-      <c r="S19" s="88"/>
-      <c r="T19" s="89"/>
-    </row>
-    <row r="20" s="55" customFormat="1" ht="21.4" customHeight="1" spans="1:26">
-      <c r="A20" s="95" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="95"/>
-      <c r="C20" s="96" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="95" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" s="95"/>
-      <c r="F20" s="95"/>
-      <c r="G20" s="97" t="s">
-        <v>55</v>
-      </c>
-      <c r="H20" s="98"/>
-      <c r="I20" s="98"/>
-      <c r="J20" s="99"/>
-      <c r="K20" s="100" t="s">
-        <v>56</v>
-      </c>
-      <c r="L20" s="101"/>
-      <c r="M20" s="102">
-        <v>1.4</v>
-      </c>
-      <c r="N20" s="103" t="s">
-        <v>5</v>
-      </c>
-      <c r="O20" s="104">
-        <v>0.055</v>
-      </c>
-      <c r="P20" s="104"/>
-      <c r="Q20" s="105"/>
-      <c r="R20" s="101" t="s">
-        <v>57</v>
-      </c>
-      <c r="S20" s="106"/>
-      <c r="T20" s="96" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="21" s="55" customFormat="1" ht="22.5" spans="1:26">
-      <c r="A21" s="107" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="107"/>
-      <c r="C21" s="108"/>
-      <c r="D21" s="109" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="110">
-        <v>465.3</v>
-      </c>
-      <c r="F21" s="111" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21" s="112">
-        <v>172.5</v>
-      </c>
-      <c r="H21" s="111" t="s">
-        <v>62</v>
-      </c>
-      <c r="I21" s="113">
-        <v>1</v>
-      </c>
-      <c r="J21" s="114" t="s">
-        <v>63</v>
-      </c>
-      <c r="K21" s="95" t="s">
-        <v>64</v>
-      </c>
-      <c r="L21" s="96" t="s">
-        <v>65</v>
-      </c>
-      <c r="M21" s="109" t="s">
-        <v>66</v>
-      </c>
-      <c r="N21" s="115"/>
-      <c r="O21" s="116"/>
-      <c r="P21" s="116"/>
-      <c r="Q21" s="117"/>
-      <c r="R21" s="100" t="s">
-        <v>67</v>
-      </c>
-      <c r="S21" s="106"/>
-      <c r="T21" s="78"/>
-      <c r="U21" s="118"/>
-    </row>
-    <row r="22" s="55" customFormat="1" ht="15" spans="1:26">
-      <c r="A22" s="83" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="84"/>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="84"/>
-      <c r="F22" s="84"/>
-      <c r="G22" s="84"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="84"/>
-      <c r="K22" s="84"/>
-      <c r="L22" s="84"/>
-      <c r="M22" s="84"/>
-      <c r="N22" s="84"/>
-      <c r="O22" s="84"/>
-      <c r="P22" s="84"/>
-      <c r="Q22" s="84"/>
-      <c r="R22" s="84"/>
-      <c r="S22" s="84"/>
-      <c r="T22" s="85"/>
-    </row>
-    <row r="23" s="55" customFormat="1" ht="30" customHeight="1" spans="1:26">
-      <c r="A23" s="119"/>
-      <c r="B23" s="119"/>
-      <c r="C23" s="119"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="119"/>
-      <c r="H23" s="119"/>
-      <c r="I23" s="119"/>
-      <c r="J23" s="119"/>
-      <c r="K23" s="119"/>
-      <c r="L23" s="119"/>
-      <c r="M23" s="119"/>
-      <c r="N23" s="119"/>
-      <c r="O23" s="119"/>
-      <c r="P23" s="119"/>
-      <c r="Q23" s="119"/>
-      <c r="R23" s="119"/>
-      <c r="S23" s="119"/>
-      <c r="T23" s="119"/>
-    </row>
-    <row r="24" s="55" customFormat="1" ht="21" customHeight="1" spans="1:26">
-      <c r="A24" s="120" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="120"/>
-      <c r="C24" s="95" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="121" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="122"/>
-      <c r="F24" s="121" t="s">
-        <v>72</v>
-      </c>
-      <c r="G24" s="123"/>
-      <c r="H24" s="123"/>
-      <c r="I24" s="123"/>
-      <c r="J24" s="122"/>
-      <c r="K24" s="100" t="s">
-        <v>73</v>
-      </c>
-      <c r="L24" s="101"/>
-      <c r="M24" s="101"/>
-      <c r="N24" s="123"/>
-      <c r="O24" s="123"/>
-      <c r="P24" s="123"/>
-      <c r="Q24" s="122"/>
-      <c r="R24" s="100" t="s">
-        <v>74</v>
-      </c>
-      <c r="S24" s="101"/>
-      <c r="T24" s="106"/>
-    </row>
-    <row r="25" s="55" customFormat="1" ht="21" customHeight="1" spans="1:26">
-      <c r="A25" s="124"/>
-      <c r="B25" s="125"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="124"/>
-      <c r="E25" s="125"/>
-      <c r="F25" s="126"/>
-      <c r="G25" s="126"/>
-      <c r="H25" s="126"/>
-      <c r="I25" s="126"/>
-      <c r="J25" s="125"/>
-      <c r="K25" s="126"/>
-      <c r="L25" s="124"/>
-      <c r="M25" s="124"/>
-      <c r="N25" s="124"/>
-      <c r="O25" s="126"/>
-      <c r="P25" s="126"/>
-      <c r="Q25" s="125"/>
-      <c r="R25" s="127"/>
-      <c r="S25" s="127"/>
-      <c r="T25" s="128"/>
-    </row>
-    <row r="26" s="55" customFormat="1" ht="15" spans="1:26">
-      <c r="A26" s="129"/>
-      <c r="B26" s="130"/>
-      <c r="C26" s="129"/>
-      <c r="D26" s="129"/>
-      <c r="E26" s="130"/>
-      <c r="F26" s="131"/>
-      <c r="G26" s="131"/>
-      <c r="H26" s="131"/>
-      <c r="I26" s="131"/>
-      <c r="J26" s="130"/>
-      <c r="K26" s="131"/>
-      <c r="L26" s="129"/>
-      <c r="M26" s="129"/>
-      <c r="N26" s="129"/>
-      <c r="O26" s="131"/>
-      <c r="P26" s="131"/>
-      <c r="Q26" s="130"/>
-      <c r="R26" s="132"/>
-      <c r="S26" s="132"/>
-      <c r="T26" s="133"/>
-    </row>
-    <row r="27" s="55" customFormat="1" ht="15" spans="1:26">
-      <c r="A27" s="134"/>
-      <c r="B27" s="134"/>
-      <c r="C27" s="134"/>
-      <c r="D27" s="134"/>
-      <c r="E27" s="134"/>
-      <c r="F27" s="134"/>
-      <c r="G27" s="134"/>
-      <c r="H27" s="134"/>
-      <c r="I27" s="134"/>
-      <c r="J27" s="134"/>
-      <c r="K27" s="134"/>
-      <c r="L27" s="134"/>
-      <c r="M27" s="134"/>
-      <c r="N27" s="134"/>
-      <c r="O27" s="134"/>
-      <c r="P27" s="134"/>
-      <c r="Q27" s="134"/>
-      <c r="R27" s="135"/>
-      <c r="S27" s="135"/>
-      <c r="T27" s="135"/>
-    </row>
-    <row r="28" ht="25" customHeight="1" spans="1:26">
-      <c r="A28" s="2"/>
-      <c r="B28" s="57"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="N28" s="60"/>
-      <c r="O28" s="60"/>
-      <c r="P28" s="60"/>
-      <c r="Q28" s="60"/>
-      <c r="R28" s="59" t="s">
-        <v>2</v>
-      </c>
-      <c r="S28" s="59"/>
-      <c r="T28" s="59"/>
-    </row>
-    <row r="29" ht="25" customHeight="1" spans="1:26">
-      <c r="A29" s="61"/>
-      <c r="B29" s="62"/>
-      <c r="C29" s="63"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="64" t="s">
-        <v>3</v>
-      </c>
-      <c r="N29" s="65" t="s">
-        <v>4</v>
-      </c>
-      <c r="O29" s="65"/>
-      <c r="P29" s="66" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q29" s="67" t="s">
-        <v>6</v>
-      </c>
-      <c r="R29" s="68"/>
-      <c r="S29" s="69"/>
-      <c r="T29" s="69"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="24" customHeight="1" spans="1:26">
-      <c r="A30" s="136" t="s">
-        <v>75</v>
-      </c>
-      <c r="B30" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="50" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="50"/>
-      <c r="J30" s="50"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="50"/>
-      <c r="M30" s="136" t="s">
-        <v>79</v>
-      </c>
-      <c r="N30" s="136"/>
-      <c r="O30" s="50" t="s">
-        <v>80</v>
-      </c>
-      <c r="P30" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="50"/>
-      <c r="S30" s="50"/>
-      <c r="T30" s="50"/>
-    </row>
-    <row r="31" s="56" customFormat="1" ht="72" spans="1:26">
-      <c r="A31" s="137">
+    <row r="4" s="53" customFormat="1" ht="81.5" spans="1:26">
+      <c r="A4" s="68">
         <v>10</v>
       </c>
-      <c r="B31" s="138" t="str">
-        <f>CONCATENATE(X31,CHAR(10),Y31)</f>
+      <c r="B4" s="69" t="str">
+        <f>CONCATENATE(X4,CHAR(10),Y4)</f>
         <v>钣金领料
 SM Incoming Inspection</v>
       </c>
-      <c r="C31" s="137" t="s">
-        <v>5</v>
-      </c>
-      <c r="D31" s="139" t="s">
-        <v>82</v>
-      </c>
-      <c r="E31" s="138"/>
-      <c r="F31" s="138"/>
-      <c r="G31" s="138"/>
-      <c r="H31" s="138"/>
-      <c r="I31" s="138"/>
-      <c r="J31" s="138"/>
-      <c r="K31" s="138"/>
-      <c r="L31" s="138"/>
-      <c r="M31" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N31" s="140"/>
-      <c r="O31" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="P31" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q31" s="141"/>
-      <c r="R31" s="141"/>
-      <c r="S31" s="141"/>
-      <c r="T31" s="141"/>
-      <c r="X31" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z31" s="56" t="str">
-        <f>D31</f>
+      <c r="C4" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="69"/>
+      <c r="F4" s="69"/>
+      <c r="G4" s="69"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="69"/>
+      <c r="K4" s="69"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" s="70"/>
+      <c r="O4" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P4" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q4" s="71"/>
+      <c r="R4" s="71"/>
+      <c r="S4" s="71"/>
+      <c r="T4" s="71"/>
+      <c r="X4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z4" s="53" t="str">
+        <f>D4</f>
         <v>按FT检查来料的牌号/状态、规格、批号和表面状态；
 Inspect incoming material specification/condition, size, lot number and surface quality per FT;
 材料代用单号：___________________
 Material Substitution Sheet NO:</v>
       </c>
     </row>
-    <row r="32" s="56" customFormat="1" ht="72" spans="1:26">
-      <c r="A32" s="137">
+    <row r="5" s="53" customFormat="1" ht="81.5" spans="1:26">
+      <c r="A5" s="68">
         <v>20</v>
       </c>
-      <c r="B32" s="138" t="str">
-        <f t="shared" ref="B32:B37" si="0">CONCATENATE(X32,CHAR(10),Y32)</f>
+      <c r="B5" s="69" t="str">
+        <f t="shared" ref="B5:B10" si="0">CONCATENATE(X5,CHAR(10),Y5)</f>
         <v>法国数控叠料下料铣床钣金下料
 NC Routing</v>
       </c>
-      <c r="C32" s="137" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="138" t="s">
-        <v>88</v>
-      </c>
-      <c r="E32" s="138"/>
-      <c r="F32" s="138"/>
-      <c r="G32" s="138"/>
-      <c r="H32" s="138"/>
-      <c r="I32" s="138"/>
-      <c r="J32" s="138"/>
-      <c r="K32" s="138"/>
-      <c r="L32" s="138"/>
-      <c r="M32" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N32" s="140"/>
-      <c r="O32" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="P32" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q32" s="141"/>
-      <c r="R32" s="141"/>
-      <c r="S32" s="141"/>
-      <c r="T32" s="141"/>
-      <c r="X32" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>90</v>
-      </c>
-      <c r="Z32" s="56" t="str">
-        <f t="shared" ref="Z32:Z34" si="1">D32</f>
+      <c r="C5" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="69" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="69"/>
+      <c r="F5" s="69"/>
+      <c r="G5" s="69"/>
+      <c r="H5" s="69"/>
+      <c r="I5" s="69"/>
+      <c r="J5" s="69"/>
+      <c r="K5" s="69"/>
+      <c r="L5" s="69"/>
+      <c r="M5" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="70"/>
+      <c r="O5" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P5" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="71"/>
+      <c r="X5" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z5" s="53" t="str">
+        <f t="shared" ref="Z5:Z7" si="1">D5</f>
         <v>按照AIPS03-11-001及XA-OI-0310-01使用数控下料铣铣制外形及孔(参照草图1)，展开数据集E53234023200-01。
 Milling the profile and hole according to AIPS03-11-001 and XA-OI-0310-01(See sketch 1), unfolded data E53234023200-01.</v>
       </c>
     </row>
-    <row r="33" s="56" customFormat="1" ht="72" spans="1:26">
-      <c r="A33" s="137">
+    <row r="6" s="53" customFormat="1" ht="81.5" spans="1:26">
+      <c r="A6" s="68">
         <v>30</v>
       </c>
-      <c r="B33" s="138" t="str">
+      <c r="B6" s="69" t="str">
         <f t="shared" si="0"/>
         <v>钣金钳工（新）
 Benchwork</v>
       </c>
-      <c r="C33" s="137" t="s">
-        <v>91</v>
-      </c>
-      <c r="D33" s="138" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" s="138"/>
-      <c r="F33" s="138"/>
-      <c r="G33" s="138"/>
-      <c r="H33" s="138"/>
-      <c r="I33" s="138"/>
-      <c r="J33" s="138"/>
-      <c r="K33" s="138"/>
-      <c r="L33" s="138"/>
-      <c r="M33" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N33" s="140"/>
-      <c r="O33" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="P33" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q33" s="141"/>
-      <c r="R33" s="141"/>
-      <c r="S33" s="141"/>
-      <c r="T33" s="141"/>
-      <c r="X33" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>94</v>
-      </c>
-      <c r="Z33" s="56" t="str">
+      <c r="C6" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="69" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" s="70"/>
+      <c r="O6" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P6" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q6" s="71"/>
+      <c r="R6" s="71"/>
+      <c r="S6" s="71"/>
+      <c r="T6" s="71"/>
+      <c r="X6" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="53" t="str">
         <f t="shared" si="1"/>
         <v>按文件ADET0031和XA-OI-0311-01去除零件毛刺。
 Deburring around the edge of the part  according to ADET0031 and XA-OI-0311-01.</v>
       </c>
     </row>
-    <row r="34" s="56" customFormat="1" ht="72" spans="1:26">
-      <c r="A34" s="137">
+    <row r="7" s="53" customFormat="1" ht="81.5" spans="1:26">
+      <c r="A7" s="68">
         <v>40</v>
       </c>
-      <c r="B34" s="138" t="str">
+      <c r="B7" s="69" t="str">
         <f t="shared" si="0"/>
         <v>钣金下料检验
 SM inspection</v>
       </c>
-      <c r="C34" s="137" t="s">
-        <v>91</v>
-      </c>
-      <c r="D34" s="138" t="s">
-        <v>95</v>
-      </c>
-      <c r="E34" s="138"/>
-      <c r="F34" s="138"/>
-      <c r="G34" s="138"/>
-      <c r="H34" s="138"/>
-      <c r="I34" s="138"/>
-      <c r="J34" s="138"/>
-      <c r="K34" s="138"/>
-      <c r="L34" s="138"/>
-      <c r="M34" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N34" s="140"/>
-      <c r="O34" s="141" t="s">
-        <v>96</v>
-      </c>
-      <c r="P34" s="141" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q34" s="141"/>
-      <c r="R34" s="141"/>
-      <c r="S34" s="141"/>
-      <c r="T34" s="141"/>
-      <c r="X34" t="s">
-        <v>98</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z34" s="56" t="str">
+      <c r="C7" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="69" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" s="70"/>
+      <c r="O7" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="71" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q7" s="71"/>
+      <c r="R7" s="71"/>
+      <c r="S7" s="71"/>
+      <c r="T7" s="71"/>
+      <c r="X7" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z7" s="53" t="str">
         <f t="shared" si="1"/>
         <v>1、按XA-QI-0314 进行手工测量;
 Semi-Finished Inspection per XA-QI-0314</v>
       </c>
     </row>
-    <row r="35" s="56" customFormat="1" ht="72" customHeight="1" spans="1:26">
-      <c r="A35" s="137">
+    <row r="8" s="53" customFormat="1" ht="72" customHeight="1" spans="1:26">
+      <c r="A8" s="68">
         <v>50</v>
       </c>
-      <c r="B35" s="138" t="str">
+      <c r="B8" s="69" t="str">
         <f t="shared" si="0"/>
         <v>通用铝合金手工清洗
 Cleaning of aluminum alloys</v>
       </c>
-      <c r="C35" s="137" t="s">
-        <v>5</v>
-      </c>
-      <c r="D35" s="138" t="s">
-        <v>100</v>
-      </c>
-      <c r="E35" s="138"/>
-      <c r="F35" s="138"/>
-      <c r="G35" s="138"/>
-      <c r="H35" s="138"/>
-      <c r="I35" s="138"/>
-      <c r="J35" s="138"/>
-      <c r="K35" s="138"/>
-      <c r="L35" s="138"/>
-      <c r="M35" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N35" s="140"/>
-      <c r="O35" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="P35" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q35" s="141"/>
-      <c r="R35" s="141"/>
-      <c r="S35" s="141"/>
-      <c r="T35" s="141"/>
-      <c r="X35" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>102</v>
-      </c>
-      <c r="Z35" s="56" t="str">
-        <f t="shared" ref="Z35:Z47" si="2">D35</f>
+      <c r="C8" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="69" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="69"/>
+      <c r="K8" s="69"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" s="70"/>
+      <c r="O8" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P8" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q8" s="71"/>
+      <c r="R8" s="71"/>
+      <c r="S8" s="71"/>
+      <c r="T8" s="71"/>
+      <c r="X8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z8" s="53" t="str">
+        <f t="shared" ref="Z8:Z20" si="2">D8</f>
         <v>清洗按照XA-OI-0401/AIPI09-01-002进行;
 Cleaning of aluminum alloys  Cleaning per XA-OI-0401/AIPI09-01-002</v>
       </c>
     </row>
-    <row r="36" s="56" customFormat="1" ht="126.75" customHeight="1" spans="1:26">
-      <c r="A36" s="137">
+    <row r="9" s="53" customFormat="1" ht="126.75" customHeight="1" spans="1:26">
+      <c r="A9" s="68">
         <v>60</v>
       </c>
-      <c r="B36" s="138" t="str">
+      <c r="B9" s="69" t="str">
         <f t="shared" si="0"/>
         <v>AIPS/AIPI铝合金的固溶
 Solution</v>
       </c>
-      <c r="C36" s="137" t="s">
-        <v>5</v>
-      </c>
-      <c r="D36" s="138" t="s">
-        <v>103</v>
-      </c>
-      <c r="E36" s="138"/>
-      <c r="F36" s="138"/>
-      <c r="G36" s="138"/>
-      <c r="H36" s="138"/>
-      <c r="I36" s="138"/>
-      <c r="J36" s="138"/>
-      <c r="K36" s="138"/>
-      <c r="L36" s="138"/>
-      <c r="M36" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N36" s="140"/>
-      <c r="O36" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="P36" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q36" s="141"/>
-      <c r="R36" s="141"/>
-      <c r="S36" s="141"/>
-      <c r="T36" s="141"/>
-      <c r="X36" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>105</v>
-      </c>
-      <c r="Z36" s="56" t="str">
+      <c r="C9" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="69" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="69"/>
+      <c r="K9" s="69"/>
+      <c r="L9" s="69"/>
+      <c r="M9" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N9" s="70"/>
+      <c r="O9" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P9" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q9" s="71"/>
+      <c r="R9" s="71"/>
+      <c r="S9" s="71"/>
+      <c r="T9" s="71"/>
+      <c r="X9" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z9" s="53" t="str">
         <f t="shared" si="2"/>
         <v>1.按文件XA-OI-0401和AIPI04-01-001进行固溶处理，将零件处理到W状态。保温温度为(495±5)℃，保温时间(35±5)min，淬火水温15℃～32℃，淬火过程水温不超过10℃，淬火后，水温≤37.8℃，淬火转移时间≤10秒。调用编号0020程序
 Solution treatment to “W” condition according to XA-OI-0401 and AIPI04-01-001. Temperature is (495±5)℃, soaking time is(35±5)min, quenching in water and initial water temperature is in a range of 15℃～32℃, water temperature shall not rise by more than 10℃ and final temperature less than 37.8℃, maximum quench delay is 10 seconds.Call program No. 0020.
@@ -7594,150 +5339,150 @@
 Inspect according to XA-QI-0401.</v>
       </c>
     </row>
-    <row r="37" s="56" customFormat="1" ht="72" spans="1:26">
-      <c r="A37" s="137">
+    <row r="10" s="53" customFormat="1" ht="81.5" spans="1:26">
+      <c r="A10" s="68">
         <v>70</v>
       </c>
-      <c r="B37" s="138" t="str">
+      <c r="B10" s="69" t="str">
         <f t="shared" si="0"/>
         <v>通用冷藏
 Refrigerate</v>
       </c>
-      <c r="C37" s="137" t="s">
-        <v>5</v>
-      </c>
-      <c r="D37" s="138" t="s">
-        <v>106</v>
-      </c>
-      <c r="E37" s="138"/>
-      <c r="F37" s="138"/>
-      <c r="G37" s="138"/>
-      <c r="H37" s="138"/>
-      <c r="I37" s="138"/>
-      <c r="J37" s="138"/>
-      <c r="K37" s="138"/>
-      <c r="L37" s="138"/>
-      <c r="M37" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N37" s="140"/>
-      <c r="O37" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="P37" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q37" s="141"/>
-      <c r="R37" s="141"/>
-      <c r="S37" s="141"/>
-      <c r="T37" s="141"/>
-      <c r="X37" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y37" t="s">
-        <v>108</v>
-      </c>
-      <c r="Z37" s="56" t="str">
-        <f t="shared" ref="Z37" si="3">D37</f>
+      <c r="C10" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="69" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="69"/>
+      <c r="K10" s="69"/>
+      <c r="L10" s="69"/>
+      <c r="M10" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N10" s="70"/>
+      <c r="O10" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P10" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="71"/>
+      <c r="S10" s="71"/>
+      <c r="T10" s="71"/>
+      <c r="X10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z10" s="53" t="str">
+        <f t="shared" ref="Z10" si="3">D10</f>
         <v>1.按文件XA-OI-0401进行冷藏，并在冷藏记录和“W状态成形/校形记录”中填写质量记录。
 Refrigerated storage parts according to XA-OI-0401，and fill the quality records in refrigeration record and “W” Condition Forming/Straightening Record.
 2.按文件XA-QI-0401进行检验。
 Inspect according to XA-QI-0401.</v>
       </c>
     </row>
-    <row r="38" s="56" customFormat="1" ht="72" spans="1:26">
-      <c r="A38" s="137">
+    <row r="11" s="53" customFormat="1" ht="81.5" spans="1:26">
+      <c r="A11" s="68">
         <v>80</v>
       </c>
-      <c r="B38" s="138" t="str">
-        <f t="shared" ref="B38:B47" si="4">CONCATENATE(X38,CHAR(10),Y38)</f>
+      <c r="B11" s="69" t="str">
+        <f t="shared" ref="B11:B20" si="4">CONCATENATE(X11,CHAR(10),Y11)</f>
         <v>橡皮囊液压成型机液压
 Hydraulic Forming</v>
       </c>
-      <c r="C38" s="137" t="s">
-        <v>109</v>
-      </c>
-      <c r="D38" s="138" t="s">
-        <v>110</v>
-      </c>
-      <c r="E38" s="138"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="138"/>
-      <c r="H38" s="138"/>
-      <c r="I38" s="138"/>
-      <c r="J38" s="138"/>
-      <c r="K38" s="138"/>
-      <c r="L38" s="138"/>
-      <c r="M38" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N38" s="140"/>
-      <c r="O38" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="P38" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q38" s="141"/>
-      <c r="R38" s="141"/>
-      <c r="S38" s="141"/>
-      <c r="T38" s="141"/>
-      <c r="X38" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>112</v>
-      </c>
-      <c r="Z38" s="56" t="str">
+      <c r="C11" s="68" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="69"/>
+      <c r="K11" s="69"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N11" s="70"/>
+      <c r="O11" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P11" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="71"/>
+      <c r="X11" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z11" s="53" t="str">
         <f t="shared" si="2"/>
         <v>按文件AIPS 03-10-005以及 XA-OI-0312-02，根据草图1将展开料液压成形，符合图纸的要求。
 Hydraulic forming the developed material according to AIPS 03-10-005 and XA-OI-0312-02 to meet the requirements of drawing. See sketch 1.</v>
       </c>
     </row>
-    <row r="39" s="56" customFormat="1" ht="104.25" customHeight="1" spans="1:26">
-      <c r="A39" s="137">
+    <row r="12" s="53" customFormat="1" ht="104.25" customHeight="1" spans="1:26">
+      <c r="A12" s="68">
         <v>90</v>
       </c>
-      <c r="B39" s="138" t="str">
+      <c r="B12" s="69" t="str">
         <f t="shared" si="4"/>
         <v>钣金校形
 Dress</v>
       </c>
-      <c r="C39" s="137" t="s">
-        <v>91</v>
-      </c>
-      <c r="D39" s="138" t="s">
-        <v>113</v>
-      </c>
-      <c r="E39" s="138"/>
-      <c r="F39" s="138"/>
-      <c r="G39" s="138"/>
-      <c r="H39" s="138"/>
-      <c r="I39" s="138"/>
-      <c r="J39" s="138"/>
-      <c r="K39" s="138"/>
-      <c r="L39" s="138"/>
-      <c r="M39" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N39" s="140"/>
-      <c r="O39" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="P39" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q39" s="141"/>
-      <c r="R39" s="141"/>
-      <c r="S39" s="141"/>
-      <c r="T39" s="141"/>
-      <c r="X39" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y39" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z39" s="56" t="str">
+      <c r="C12" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="69"/>
+      <c r="K12" s="69"/>
+      <c r="L12" s="69"/>
+      <c r="M12" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N12" s="70"/>
+      <c r="O12" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P12" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q12" s="71"/>
+      <c r="R12" s="71"/>
+      <c r="S12" s="71"/>
+      <c r="T12" s="71"/>
+      <c r="X12" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z12" s="53" t="str">
         <f t="shared" si="2"/>
         <v>淬火后，零件在-1℃～37.8℃保持W状态的最长时间为30分钟。冷藏温度在-18℃以下，保存时间不能超过7天。在“W状态成形/校形记录”中填写质量记录。
 Reach -1℃ to 37.8℃ after quenching, maximum time held in w condition is 30min. Storage temperature below -18℃ and storage time is less than 7 days. Fill the quality record in “W” Condition Forming/Straightening Record.
@@ -7745,99 +5490,99 @@
 Straightening  parts according to AIPS 03-10-005  and XA-OI-0312-01to meet the requirments of drawing and tolerance.</v>
       </c>
     </row>
-    <row r="40" s="56" customFormat="1" ht="72" customHeight="1" spans="1:26">
-      <c r="A40" s="137">
+    <row r="13" s="53" customFormat="1" ht="72" customHeight="1" spans="1:26">
+      <c r="A13" s="68">
         <v>100</v>
       </c>
-      <c r="B40" s="138" t="str">
+      <c r="B13" s="69" t="str">
         <f t="shared" si="4"/>
         <v>钣金成型检验
 SM inspection</v>
       </c>
-      <c r="C40" s="137" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40" s="138" t="s">
-        <v>116</v>
-      </c>
-      <c r="E40" s="138"/>
-      <c r="F40" s="138"/>
-      <c r="G40" s="138"/>
-      <c r="H40" s="138"/>
-      <c r="I40" s="138"/>
-      <c r="J40" s="138"/>
-      <c r="K40" s="138"/>
-      <c r="L40" s="138"/>
-      <c r="M40" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N40" s="140"/>
-      <c r="O40" s="141" t="s">
-        <v>96</v>
-      </c>
-      <c r="P40" s="141" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q40" s="141"/>
-      <c r="R40" s="141"/>
-      <c r="S40" s="141"/>
-      <c r="T40" s="141"/>
-      <c r="X40" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y40" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z40" s="56" t="str">
+      <c r="C13" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="69"/>
+      <c r="F13" s="69"/>
+      <c r="G13" s="69"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="69"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="69"/>
+      <c r="L13" s="69"/>
+      <c r="M13" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N13" s="70"/>
+      <c r="O13" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="P13" s="71" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q13" s="71"/>
+      <c r="R13" s="71"/>
+      <c r="S13" s="71"/>
+      <c r="T13" s="71"/>
+      <c r="X13" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z13" s="53" t="str">
         <f t="shared" si="2"/>
         <v>1、按XA-QI-0315 进行手工测量;
 Semi-Finished Inspection per XA-QI-0315;</v>
       </c>
     </row>
-    <row r="41" s="56" customFormat="1" ht="94.5" customHeight="1" spans="1:26">
-      <c r="A41" s="137">
+    <row r="14" s="53" customFormat="1" ht="94.5" customHeight="1" spans="1:26">
+      <c r="A14" s="68">
         <v>110</v>
       </c>
-      <c r="B41" s="138" t="str">
+      <c r="B14" s="69" t="str">
         <f t="shared" si="4"/>
         <v>电导率
 Electrical Conductivity Test</v>
       </c>
-      <c r="C41" s="137" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="138" t="s">
-        <v>118</v>
-      </c>
-      <c r="E41" s="138"/>
-      <c r="F41" s="138"/>
-      <c r="G41" s="138"/>
-      <c r="H41" s="138"/>
-      <c r="I41" s="138"/>
-      <c r="J41" s="138"/>
-      <c r="K41" s="138"/>
-      <c r="L41" s="138"/>
-      <c r="M41" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N41" s="140"/>
-      <c r="O41" s="141" t="s">
-        <v>96</v>
-      </c>
-      <c r="P41" s="141" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q41" s="141"/>
-      <c r="R41" s="141"/>
-      <c r="S41" s="141"/>
-      <c r="T41" s="141"/>
-      <c r="X41" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y41" t="s">
-        <v>120</v>
-      </c>
-      <c r="Z41" s="56" t="str">
+      <c r="C14" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="69" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="70"/>
+      <c r="O14" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="P14" s="71" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q14" s="71"/>
+      <c r="R14" s="71"/>
+      <c r="S14" s="71"/>
+      <c r="T14" s="71"/>
+      <c r="X14" t="s">
+        <v>52</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z14" s="53" t="str">
         <f t="shared" si="2"/>
         <v>在室温（15℃～40℃）保持至少96小时自然时效至T42状态后，按照XA-Lab-2301和AITM6-6004在有效测试区域内进行电导率测试，电导率满足 ：（16.5-21.5）MS/m。
 After natural aging at RT (15℃～40℃) for 96 hours minimum to T42 temper, electrical Conductivity Test in the effective test area as per XA-Lab-2301 and AITM6-6004, test value shall meet the requirement：（16.5-21.5）MS/m.
@@ -7845,50 +5590,50 @@
 测试时间/Operating time: ________________________</v>
       </c>
     </row>
-    <row r="42" s="56" customFormat="1" ht="144" customHeight="1" spans="1:26">
-      <c r="A42" s="137">
+    <row r="15" s="53" customFormat="1" ht="144" customHeight="1" spans="1:26">
+      <c r="A15" s="68">
         <v>120</v>
       </c>
-      <c r="B42" s="138" t="str">
+      <c r="B15" s="69" t="str">
         <f t="shared" si="4"/>
         <v>AIPS/AIPI酒石酸硫酸阳极化紧公差不封闭
 AIPS/AIPI unsealed TSA for tight dimensional tolerance</v>
       </c>
-      <c r="C42" s="137" t="s">
-        <v>5</v>
-      </c>
-      <c r="D42" s="138" t="s">
-        <v>121</v>
-      </c>
-      <c r="E42" s="138"/>
-      <c r="F42" s="138"/>
-      <c r="G42" s="138"/>
-      <c r="H42" s="138"/>
-      <c r="I42" s="138"/>
-      <c r="J42" s="138"/>
-      <c r="K42" s="138"/>
-      <c r="L42" s="138"/>
-      <c r="M42" s="140" t="s">
-        <v>122</v>
-      </c>
-      <c r="N42" s="140"/>
-      <c r="O42" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="P42" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q42" s="141"/>
-      <c r="R42" s="141"/>
-      <c r="S42" s="141"/>
-      <c r="T42" s="141"/>
-      <c r="X42" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y42" t="s">
-        <v>124</v>
-      </c>
-      <c r="Z42" s="56" t="str">
+      <c r="C15" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="69" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="69"/>
+      <c r="M15" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="N15" s="70"/>
+      <c r="O15" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P15" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q15" s="71"/>
+      <c r="R15" s="71"/>
+      <c r="S15" s="71"/>
+      <c r="T15" s="71"/>
+      <c r="X15" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z15" s="53" t="str">
         <f t="shared" si="2"/>
         <v>1、按照XA-OI-0201-03/AIPS 02-01-003文件要求，执行K7程序进行非紧公差、不封闭的酒石酸阳极化处理，在质量记录一列记录生产记录编号；
 Perform unsealed TSA of aluminum alloys for no tight dimensional tolerance per K7 program according to XA-OI-0201-03/AIPS 02-01-003, fill the production record No. in the quality record column.
@@ -7896,50 +5641,50 @@
 Quality inspection per XA-QI-0201.</v>
       </c>
     </row>
-    <row r="43" s="56" customFormat="1" ht="129.75" customHeight="1" spans="1:26">
-      <c r="A43" s="137">
+    <row r="16" s="53" customFormat="1" ht="129.75" customHeight="1" spans="1:26">
+      <c r="A16" s="68">
         <v>130</v>
       </c>
-      <c r="B43" s="138" t="str">
+      <c r="B16" s="69" t="str">
         <f t="shared" si="4"/>
         <v>AIPS/AIPI喷P60-A底漆
 AIPS/AIPI P60-A primer painting</v>
       </c>
-      <c r="C43" s="137" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" s="138" t="s">
-        <v>125</v>
-      </c>
-      <c r="E43" s="138"/>
-      <c r="F43" s="138"/>
-      <c r="G43" s="138"/>
-      <c r="H43" s="138"/>
-      <c r="I43" s="138"/>
-      <c r="J43" s="138"/>
-      <c r="K43" s="138"/>
-      <c r="L43" s="138"/>
-      <c r="M43" s="140" t="s">
-        <v>122</v>
-      </c>
-      <c r="N43" s="140"/>
-      <c r="O43" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="P43" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q43" s="141"/>
-      <c r="R43" s="141"/>
-      <c r="S43" s="141"/>
-      <c r="T43" s="141"/>
-      <c r="X43" t="s">
-        <v>126</v>
-      </c>
-      <c r="Y43" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z43" s="56" t="str">
+      <c r="C16" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="69" t="s">
+        <v>58</v>
+      </c>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="69"/>
+      <c r="L16" s="69"/>
+      <c r="M16" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="N16" s="70"/>
+      <c r="O16" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P16" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="71"/>
+      <c r="S16" s="71"/>
+      <c r="T16" s="71"/>
+      <c r="X16" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z16" s="53" t="str">
         <f t="shared" si="2"/>
         <v>1、阳极化后24小时之内，按照文件XA-OI-0501-03/AIPS 05-02-009文件要求，喷涂P60-A底漆，在质量记录一列记录喷漆记录编号及漆膜厚度范围值；
 P60-A primer painting per XA-OI-0501-03/AIPS 05-02-009 within 24 hours after anodizing, fill the painting record No. in the quality record column and record film thickness range.
@@ -7950,50 +5695,50 @@
 记录漆膜厚度范围值/ record the range of dry film thickness：_________________________</v>
       </c>
     </row>
-    <row r="44" s="56" customFormat="1" ht="126.75" customHeight="1" spans="1:26">
-      <c r="A44" s="137">
+    <row r="17" s="53" customFormat="1" ht="126.75" customHeight="1" spans="1:26">
+      <c r="A17" s="68">
         <v>140</v>
       </c>
-      <c r="B44" s="138" t="str">
+      <c r="B17" s="69" t="str">
         <f t="shared" si="4"/>
         <v>AIPS/AIPI喷F70-A面漆
 AIPS/AIPI F70-A topcoat painting</v>
       </c>
-      <c r="C44" s="137" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="138" t="s">
-        <v>128</v>
-      </c>
-      <c r="E44" s="138"/>
-      <c r="F44" s="138"/>
-      <c r="G44" s="138"/>
-      <c r="H44" s="138"/>
-      <c r="I44" s="138"/>
-      <c r="J44" s="138"/>
-      <c r="K44" s="138"/>
-      <c r="L44" s="138"/>
-      <c r="M44" s="140" t="s">
-        <v>122</v>
-      </c>
-      <c r="N44" s="140"/>
-      <c r="O44" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="P44" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q44" s="141"/>
-      <c r="R44" s="141"/>
-      <c r="S44" s="141"/>
-      <c r="T44" s="141"/>
-      <c r="X44" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y44" t="s">
-        <v>130</v>
-      </c>
-      <c r="Z44" s="56" t="str">
+      <c r="C17" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="69"/>
+      <c r="M17" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="N17" s="70"/>
+      <c r="O17" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P17" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="71"/>
+      <c r="T17" s="71"/>
+      <c r="X17" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z17" s="53" t="str">
         <f t="shared" si="2"/>
         <v>1、底漆喷涂后48小时内，按照文件XA-OI-0501-04/AIPS 05-02-009文件要求，喷涂F70-A面漆，在质量记录一列记录喷漆记录编号及漆膜厚度范围值；
 F70-A topcoat painting per XA-OI-0501-04/AIPS 05-02-009 within 48 hours after primer painting, fill the painting record No. in the quality record column and record film thickness range.
@@ -8004,50 +5749,50 @@
 记录漆膜厚度范围值/ record the range of dry film thickness：_________________________</v>
       </c>
     </row>
-    <row r="45" s="56" customFormat="1" ht="75.75" customHeight="1" spans="1:26">
-      <c r="A45" s="137">
+    <row r="18" s="53" customFormat="1" ht="75.75" customHeight="1" spans="1:26">
+      <c r="A18" s="68">
         <v>150</v>
       </c>
-      <c r="B45" s="138" t="str">
+      <c r="B18" s="69" t="str">
         <f t="shared" si="4"/>
         <v>喷码
 Marking</v>
       </c>
-      <c r="C45" s="137" t="s">
-        <v>5</v>
-      </c>
-      <c r="D45" s="138" t="s">
-        <v>131</v>
-      </c>
-      <c r="E45" s="138"/>
-      <c r="F45" s="138"/>
-      <c r="G45" s="138"/>
-      <c r="H45" s="138"/>
-      <c r="I45" s="138"/>
-      <c r="J45" s="138"/>
-      <c r="K45" s="138"/>
-      <c r="L45" s="138"/>
-      <c r="M45" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N45" s="140"/>
-      <c r="O45" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="P45" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q45" s="141"/>
-      <c r="R45" s="141"/>
-      <c r="S45" s="141"/>
-      <c r="T45" s="141"/>
-      <c r="X45" t="s">
-        <v>132</v>
-      </c>
-      <c r="Y45" t="s">
-        <v>133</v>
-      </c>
-      <c r="Z45" s="56" t="str">
+      <c r="C18" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="69" t="s">
+        <v>64</v>
+      </c>
+      <c r="E18" s="69"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="69"/>
+      <c r="K18" s="69"/>
+      <c r="L18" s="69"/>
+      <c r="M18" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N18" s="70"/>
+      <c r="O18" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P18" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="71"/>
+      <c r="S18" s="71"/>
+      <c r="T18" s="71"/>
+      <c r="X18" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z18" s="53" t="str">
         <f t="shared" si="2"/>
         <v>使用喷码机在草图1所示位置喷涂零件标识，按ABD0003/AIPS-08-01-001/XA-OI-0801-02执行。
 Use inkjet paint the part at the position where sketch1 indicated, operated as is seen in XA-OI-0801-02.
@@ -8055,50 +5800,50 @@
 The inspection requirement is in ABD0003/AIPS-08-01-001/XA-QI-0801-02.</v>
       </c>
     </row>
-    <row r="46" s="56" customFormat="1" ht="72" spans="1:26">
-      <c r="A46" s="137">
+    <row r="19" s="53" customFormat="1" ht="81.5" spans="1:26">
+      <c r="A19" s="68">
         <v>160</v>
       </c>
-      <c r="B46" s="138" t="str">
+      <c r="B19" s="69" t="str">
         <f t="shared" si="4"/>
         <v>零件终检
 Final Inspection</v>
       </c>
-      <c r="C46" s="137" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" s="138" t="s">
-        <v>134</v>
-      </c>
-      <c r="E46" s="138"/>
-      <c r="F46" s="138"/>
-      <c r="G46" s="138"/>
-      <c r="H46" s="138"/>
-      <c r="I46" s="138"/>
-      <c r="J46" s="138"/>
-      <c r="K46" s="138"/>
-      <c r="L46" s="138"/>
-      <c r="M46" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N46" s="140"/>
-      <c r="O46" s="141" t="s">
-        <v>96</v>
-      </c>
-      <c r="P46" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q46" s="141"/>
-      <c r="R46" s="141"/>
-      <c r="S46" s="141"/>
-      <c r="T46" s="141"/>
-      <c r="X46" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y46" t="s">
-        <v>136</v>
-      </c>
-      <c r="Z46" s="56" t="str">
+      <c r="C19" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="69"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="69"/>
+      <c r="K19" s="69"/>
+      <c r="L19" s="69"/>
+      <c r="M19" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N19" s="70"/>
+      <c r="O19" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="P19" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="71"/>
+      <c r="T19" s="71"/>
+      <c r="X19" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z19" s="53" t="str">
         <f t="shared" si="2"/>
         <v>1、按XA-QI-0313终检;
 Final Inspection per XA-QI-0313;
@@ -8106,50 +5851,50 @@
 Issue Certificate and record in the Quality Record column。</v>
       </c>
     </row>
-    <row r="47" s="56" customFormat="1" ht="72" spans="1:26">
-      <c r="A47" s="137">
+    <row r="20" s="53" customFormat="1" ht="81.5" spans="1:26">
+      <c r="A20" s="68">
         <v>170</v>
       </c>
-      <c r="B47" s="138" t="str">
+      <c r="B20" s="69" t="str">
         <f t="shared" si="4"/>
         <v>成品入库
 Storage</v>
       </c>
-      <c r="C47" s="137" t="s">
-        <v>5</v>
-      </c>
-      <c r="D47" s="138" t="s">
-        <v>137</v>
-      </c>
-      <c r="E47" s="138"/>
-      <c r="F47" s="138"/>
-      <c r="G47" s="138"/>
-      <c r="H47" s="138"/>
-      <c r="I47" s="138"/>
-      <c r="J47" s="138"/>
-      <c r="K47" s="138"/>
-      <c r="L47" s="138"/>
-      <c r="M47" s="140" t="s">
-        <v>83</v>
-      </c>
-      <c r="N47" s="140"/>
-      <c r="O47" s="141" t="s">
-        <v>84</v>
-      </c>
-      <c r="P47" s="141" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q47" s="141"/>
-      <c r="R47" s="141"/>
-      <c r="S47" s="141"/>
-      <c r="T47" s="141"/>
-      <c r="X47" t="s">
-        <v>138</v>
-      </c>
-      <c r="Y47" t="s">
-        <v>139</v>
-      </c>
-      <c r="Z47" s="56" t="str">
+      <c r="C20" s="68" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="69" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="69"/>
+      <c r="J20" s="69"/>
+      <c r="K20" s="69"/>
+      <c r="L20" s="69"/>
+      <c r="M20" s="70" t="s">
+        <v>16</v>
+      </c>
+      <c r="N20" s="70"/>
+      <c r="O20" s="71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P20" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="71"/>
+      <c r="S20" s="71"/>
+      <c r="T20" s="71"/>
+      <c r="X20" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z20" s="53" t="str">
         <f t="shared" si="2"/>
         <v>按XA-OI-1001-01将零件放入聚乙烯薄膜袋中并塑封，将零件移交至零件库房，做好零件入库记录，本记录交由品质部归档。
 Place parts in polyethylene bags and sealed according to XA-OI-1001-01,transfer the parts to partswarehouse,complete in-stock record,transfer the Traveler to Quality Department.</v>
@@ -8157,179 +5902,74 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <mergeCells count="164">
+  <mergeCells count="60">
     <mergeCell ref="M1:Q1"/>
     <mergeCell ref="R1:T1"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="N3:Q3"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="E4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="N4:Q4"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="A5:T5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:K6"/>
-    <mergeCell ref="N6:Q6"/>
-    <mergeCell ref="R6:S6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:K7"/>
-    <mergeCell ref="N7:Q7"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:K8"/>
-    <mergeCell ref="N8:Q8"/>
-    <mergeCell ref="R8:S8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:K9"/>
-    <mergeCell ref="N9:Q9"/>
-    <mergeCell ref="R9:S9"/>
-    <mergeCell ref="A10:T10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="N11:Q11"/>
-    <mergeCell ref="R11:T11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="N12:Q12"/>
-    <mergeCell ref="R12:T12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="N13:Q13"/>
-    <mergeCell ref="R13:T13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:J14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="N14:Q14"/>
-    <mergeCell ref="R14:T14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="N15:Q15"/>
-    <mergeCell ref="R15:T15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="N16:Q16"/>
-    <mergeCell ref="R16:T16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="N17:Q17"/>
-    <mergeCell ref="R17:T17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="N18:Q18"/>
-    <mergeCell ref="R18:T18"/>
-    <mergeCell ref="A19:T19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:J20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="R20:S20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="N21:Q21"/>
-    <mergeCell ref="R21:S21"/>
-    <mergeCell ref="A22:T22"/>
-    <mergeCell ref="A23:T23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="K24:Q24"/>
-    <mergeCell ref="R24:T24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:J25"/>
-    <mergeCell ref="N25:Q25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:J26"/>
-    <mergeCell ref="N26:Q26"/>
-    <mergeCell ref="M28:Q28"/>
-    <mergeCell ref="R28:T28"/>
-    <mergeCell ref="N29:O29"/>
-    <mergeCell ref="R29:T29"/>
-    <mergeCell ref="D30:L30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="P30:T30"/>
-    <mergeCell ref="D31:L31"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="P31:T31"/>
-    <mergeCell ref="D32:L32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="P32:T32"/>
-    <mergeCell ref="D33:L33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="P33:T33"/>
-    <mergeCell ref="D34:L34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="P34:T34"/>
-    <mergeCell ref="D35:L35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="P35:T35"/>
-    <mergeCell ref="D36:L36"/>
-    <mergeCell ref="M36:N36"/>
-    <mergeCell ref="P36:T36"/>
-    <mergeCell ref="D37:L37"/>
-    <mergeCell ref="M37:N37"/>
-    <mergeCell ref="P37:T37"/>
-    <mergeCell ref="D38:L38"/>
-    <mergeCell ref="M38:N38"/>
-    <mergeCell ref="P38:T38"/>
-    <mergeCell ref="D39:L39"/>
-    <mergeCell ref="M39:N39"/>
-    <mergeCell ref="P39:T39"/>
-    <mergeCell ref="D40:L40"/>
-    <mergeCell ref="M40:N40"/>
-    <mergeCell ref="P40:T40"/>
-    <mergeCell ref="D41:L41"/>
-    <mergeCell ref="M41:N41"/>
-    <mergeCell ref="P41:T41"/>
-    <mergeCell ref="D42:L42"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="P42:T42"/>
-    <mergeCell ref="D43:L43"/>
-    <mergeCell ref="M43:N43"/>
-    <mergeCell ref="P43:T43"/>
-    <mergeCell ref="D44:L44"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="P44:T44"/>
-    <mergeCell ref="D45:L45"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="P45:T45"/>
-    <mergeCell ref="D46:L46"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="P46:T46"/>
-    <mergeCell ref="D47:L47"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="P47:T47"/>
-    <mergeCell ref="A28:C29"/>
-    <mergeCell ref="D28:L29"/>
+    <mergeCell ref="D3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="P3:T3"/>
+    <mergeCell ref="D4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P4:T4"/>
+    <mergeCell ref="D5:L5"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="P5:T5"/>
+    <mergeCell ref="D6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="P6:T6"/>
+    <mergeCell ref="D7:L7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="P7:T7"/>
+    <mergeCell ref="D8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="P8:T8"/>
+    <mergeCell ref="D9:L9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="P9:T9"/>
+    <mergeCell ref="D10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="P10:T10"/>
+    <mergeCell ref="D11:L11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="P11:T11"/>
+    <mergeCell ref="D12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="P12:T12"/>
+    <mergeCell ref="D13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="P13:T13"/>
+    <mergeCell ref="D14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="P14:T14"/>
+    <mergeCell ref="D15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="P15:T15"/>
+    <mergeCell ref="D16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="P16:T16"/>
+    <mergeCell ref="D17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="P17:T17"/>
+    <mergeCell ref="D18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="P18:T18"/>
+    <mergeCell ref="D19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="P19:T19"/>
+    <mergeCell ref="D20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="P20:T20"/>
     <mergeCell ref="A1:C2"/>
-    <mergeCell ref="R25:T26"/>
     <mergeCell ref="D1:L2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15748031496063" right="0.15748031496063" top="0.748031496062992" bottom="0.47244094488189" header="0.31496062992126" footer="0.31496062992126"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageSetup paperSize="9" scale="35" fitToWidth="0" orientation="landscape"/>
   <headerFooter>
     <oddFooter>&amp;L★ F010204-01[6] &amp;RPage &amp;P of &amp;N</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8337,43 +5977,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="5" width="11.725" style="9" customWidth="1"/>
-    <col min="6" max="6" width="21.2666666666667" style="9" customWidth="1"/>
-    <col min="7" max="7" width="15.3666666666667" style="48" customWidth="1"/>
-    <col min="8" max="8" width="10.725" style="9" customWidth="1"/>
-    <col min="9" max="9" width="25.6333333333333" style="9" customWidth="1"/>
-    <col min="10" max="10" width="1.63333333333333" style="9" customWidth="1"/>
-    <col min="11" max="11" width="8.45" style="9" customWidth="1"/>
-    <col min="12" max="12" width="8.36666666666667" customWidth="1"/>
+    <col min="1" max="5" width="11.7272727272727" style="9" customWidth="1"/>
+    <col min="6" max="6" width="21.2636363636364" style="9" customWidth="1"/>
+    <col min="7" max="7" width="15.3636363636364" style="47" customWidth="1"/>
+    <col min="8" max="8" width="10.7272727272727" style="9" customWidth="1"/>
+    <col min="9" max="9" width="25.6363636363636" style="9" customWidth="1"/>
+    <col min="10" max="10" width="1.63636363636364" style="9" customWidth="1"/>
+    <col min="11" max="11" width="8.44545454545455" style="9" customWidth="1"/>
+    <col min="12" max="12" width="8.36363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:12">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="4" t="s">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="I1" s="6" t="str">
-        <f>首页及工序页!N2</f>
-        <v>E53234023200-01</v>
+        <v>74</v>
+      </c>
+      <c r="I1" s="6" t="e">
+        <f>首页及工序页!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="8" t="str">
-        <f>首页及工序页!Q2</f>
-        <v>A4</v>
+        <v>6</v>
+      </c>
+      <c r="K1" s="8" t="e">
+        <f>首页及工序页!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="L1" s="9"/>
     </row>
@@ -8385,7 +6025,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="4" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
@@ -8394,7 +6034,7 @@
       <c r="L2" s="9"/>
     </row>
     <row r="3" ht="25.5" customHeight="1" spans="1:12">
-      <c r="A3" s="52"/>
+      <c r="A3" s="51"/>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
       <c r="D3" s="12"/>
@@ -8405,27 +6045,27 @@
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
       <c r="K3" s="12"/>
-      <c r="L3" s="49"/>
+      <c r="L3" s="48"/>
     </row>
     <row r="4" ht="27" customHeight="1" spans="1:12">
-      <c r="A4" s="50" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
+      <c r="A4" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
       <c r="L4" s="9"/>
     </row>
     <row r="5" ht="297" customHeight="1" spans="1:12">
       <c r="A5" s="16" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -8440,21 +6080,21 @@
       <c r="L5" s="9"/>
     </row>
     <row r="6" ht="23.15" customHeight="1" spans="1:12">
-      <c r="A6" s="53" t="s">
-        <v>145</v>
-      </c>
-      <c r="B6" s="54" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
+      <c r="A6" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
       <c r="L6" s="9"/>
     </row>
   </sheetData>
@@ -8481,43 +6121,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L6"/>
-  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="5" width="11.725" style="9" customWidth="1"/>
-    <col min="6" max="6" width="21.2666666666667" style="9" customWidth="1"/>
-    <col min="7" max="7" width="15.3666666666667" style="48" customWidth="1"/>
-    <col min="8" max="8" width="10.725" style="9" customWidth="1"/>
-    <col min="9" max="9" width="25.6333333333333" style="9" customWidth="1"/>
-    <col min="10" max="10" width="1.63333333333333" style="9" customWidth="1"/>
-    <col min="11" max="11" width="8.45" style="9" customWidth="1"/>
-    <col min="12" max="12" width="8.36666666666667" customWidth="1"/>
+    <col min="1" max="5" width="11.7272727272727" style="9" customWidth="1"/>
+    <col min="6" max="6" width="21.2636363636364" style="9" customWidth="1"/>
+    <col min="7" max="7" width="15.3636363636364" style="47" customWidth="1"/>
+    <col min="8" max="8" width="10.7272727272727" style="9" customWidth="1"/>
+    <col min="9" max="9" width="25.6363636363636" style="9" customWidth="1"/>
+    <col min="10" max="10" width="1.63636363636364" style="9" customWidth="1"/>
+    <col min="11" max="11" width="8.44545454545455" style="9" customWidth="1"/>
+    <col min="12" max="12" width="8.36363636363636" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:12">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="4" t="s">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="I1" s="6" t="str">
-        <f>首页及工序页!N2</f>
-        <v>E53234023200-01</v>
+        <v>74</v>
+      </c>
+      <c r="I1" s="6" t="e">
+        <f>首页及工序页!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="8" t="str">
-        <f>首页及工序页!Q2</f>
-        <v>A4</v>
+        <v>6</v>
+      </c>
+      <c r="K1" s="8" t="e">
+        <f>首页及工序页!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="L1" s="9"/>
     </row>
@@ -8529,7 +6169,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="4" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
@@ -8539,7 +6179,7 @@
     </row>
     <row r="3" ht="25.5" customHeight="1" spans="1:12">
       <c r="A3" s="12" t="s">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -8551,27 +6191,27 @@
       <c r="I3" s="12"/>
       <c r="J3" s="12"/>
       <c r="K3" s="12"/>
-      <c r="L3" s="49"/>
+      <c r="L3" s="48"/>
     </row>
     <row r="4" ht="27" customHeight="1" spans="1:12">
-      <c r="A4" s="50" t="s">
-        <v>143</v>
-      </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
+      <c r="A4" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
       <c r="L4" s="9"/>
     </row>
     <row r="5" ht="297" customHeight="1" spans="1:12">
       <c r="A5" s="16" t="s">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -8586,21 +6226,21 @@
       <c r="L5" s="9"/>
     </row>
     <row r="6" ht="23.15" customHeight="1" spans="1:12">
-      <c r="A6" s="50" t="s">
-        <v>149</v>
-      </c>
-      <c r="B6" s="51" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
+      <c r="A6" s="49" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
+      <c r="K6" s="50"/>
       <c r="L6" s="9"/>
     </row>
   </sheetData>
@@ -8627,232 +6267,232 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="5" width="11.725" style="21" customWidth="1"/>
-    <col min="6" max="6" width="21.2666666666667" style="21" customWidth="1"/>
-    <col min="7" max="7" width="15.3666666666667" style="22" customWidth="1"/>
-    <col min="8" max="8" width="10.725" style="21" customWidth="1"/>
-    <col min="9" max="9" width="25.6333333333333" style="21" customWidth="1"/>
-    <col min="10" max="10" width="1.63333333333333" style="21" customWidth="1"/>
-    <col min="11" max="11" width="8.45" style="21" customWidth="1"/>
-    <col min="12" max="12" width="8.36666666666667" style="23" customWidth="1"/>
-    <col min="13" max="16384" width="8.725" style="23"/>
+    <col min="1" max="5" width="11.7272727272727" style="20" customWidth="1"/>
+    <col min="6" max="6" width="21.2636363636364" style="20" customWidth="1"/>
+    <col min="7" max="7" width="15.3636363636364" style="21" customWidth="1"/>
+    <col min="8" max="8" width="10.7272727272727" style="20" customWidth="1"/>
+    <col min="9" max="9" width="25.6363636363636" style="20" customWidth="1"/>
+    <col min="10" max="10" width="1.63636363636364" style="20" customWidth="1"/>
+    <col min="11" max="11" width="8.44545454545455" style="20" customWidth="1"/>
+    <col min="12" max="12" width="8.36363636363636" style="22" customWidth="1"/>
+    <col min="13" max="16384" width="8.72727272727273" style="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:12">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="H1" s="27" t="s">
-        <v>141</v>
-      </c>
-      <c r="I1" s="28" t="str">
-        <f>首页及工序页!N2</f>
-        <v>E53234023200-01</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="30" t="str">
-        <f>首页及工序页!Q2</f>
-        <v>A4</v>
-      </c>
-      <c r="L1" s="21"/>
+      <c r="A1" s="23"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="27" t="e">
+        <f>首页及工序页!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="29" t="e">
+        <f>首页及工序页!#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="L1" s="20"/>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:12">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="21"/>
+      <c r="A2" s="23"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="20"/>
     </row>
-    <row r="3" s="20" customFormat="1" ht="34.5" customHeight="1" spans="1:12">
-      <c r="A3" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="33"/>
-      <c r="J3" s="33"/>
-      <c r="K3" s="33"/>
-      <c r="L3" s="34"/>
+    <row r="3" s="19" customFormat="1" ht="34.5" customHeight="1" spans="1:12">
+      <c r="A3" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="33"/>
     </row>
-    <row r="4" s="20" customFormat="1" ht="50.15" customHeight="1" spans="1:12">
-      <c r="A4" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="F4" s="37"/>
-      <c r="G4" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="H4" s="37"/>
-      <c r="I4" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="J4" s="36" t="s">
-        <v>154</v>
-      </c>
-      <c r="K4" s="37"/>
-      <c r="L4" s="39"/>
+    <row r="4" s="19" customFormat="1" ht="50.15" customHeight="1" spans="1:12">
+      <c r="A4" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="36"/>
+      <c r="D4" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="35" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="36"/>
+      <c r="G4" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="36"/>
+      <c r="I4" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="J4" s="35" t="s">
+        <v>86</v>
+      </c>
+      <c r="K4" s="36"/>
+      <c r="L4" s="38"/>
     </row>
-    <row r="5" s="20" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
-      <c r="A5" s="35"/>
-      <c r="B5" s="36"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="39"/>
+    <row r="5" s="19" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
+      <c r="A5" s="34"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="38"/>
     </row>
-    <row r="6" s="20" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
-      <c r="A6" s="38" t="s">
-        <v>157</v>
-      </c>
-      <c r="B6" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="38" t="s">
-        <v>159</v>
-      </c>
-      <c r="E6" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="F6" s="40"/>
-      <c r="G6" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="H6" s="40"/>
-      <c r="I6" s="38" t="s">
-        <v>153</v>
-      </c>
-      <c r="J6" s="36" t="s">
-        <v>161</v>
-      </c>
-      <c r="K6" s="37"/>
-      <c r="L6" s="39"/>
+    <row r="6" s="19" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
+      <c r="A6" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="39"/>
+      <c r="D6" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="F6" s="39"/>
+      <c r="G6" s="35" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="39"/>
+      <c r="I6" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="J6" s="35" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" s="36"/>
+      <c r="L6" s="38"/>
     </row>
-    <row r="7" s="20" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
-      <c r="A7" s="41"/>
-      <c r="B7" s="42"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="45"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="47"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="37"/>
-      <c r="L7" s="39"/>
+    <row r="7" s="19" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
+      <c r="A7" s="40"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="38"/>
     </row>
-    <row r="8" s="20" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
-      <c r="A8" s="41"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="47"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="39"/>
+    <row r="8" s="19" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
+      <c r="A8" s="40"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="44"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="38"/>
     </row>
-    <row r="9" s="20" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
-      <c r="A9" s="41"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="39"/>
+    <row r="9" s="19" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
+      <c r="A9" s="40"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="38"/>
     </row>
-    <row r="10" s="20" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
-      <c r="A10" s="41"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="43"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="39"/>
+    <row r="10" s="19" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
+      <c r="A10" s="40"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="38"/>
     </row>
-    <row r="11" s="20" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
-      <c r="A11" s="41"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="45"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="43"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="37"/>
-      <c r="L11" s="39"/>
+    <row r="11" s="19" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
+      <c r="A11" s="40"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="44"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="38"/>
     </row>
-    <row r="12" s="20" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
-      <c r="A12" s="41"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="37"/>
-      <c r="L12" s="39"/>
+    <row r="12" s="19" customFormat="1" ht="40.5" customHeight="1" spans="1:12">
+      <c r="A12" s="40"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="44"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="40">
@@ -8911,43 +6551,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="8.725" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="4" width="11.725" customWidth="1"/>
+    <col min="1" max="4" width="11.7272727272727" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="11.45" customWidth="1"/>
-    <col min="7" max="7" width="16.0916666666667" customWidth="1"/>
-    <col min="8" max="8" width="10.725" customWidth="1"/>
-    <col min="9" max="9" width="26.0916666666667" customWidth="1"/>
-    <col min="10" max="10" width="2.90833333333333" customWidth="1"/>
-    <col min="11" max="11" width="9.09166666666667" customWidth="1"/>
+    <col min="6" max="6" width="11.4454545454545" customWidth="1"/>
+    <col min="7" max="7" width="16.0909090909091" customWidth="1"/>
+    <col min="8" max="8" width="10.7272727272727" customWidth="1"/>
+    <col min="9" max="9" width="26.0909090909091" customWidth="1"/>
+    <col min="10" max="10" width="2.90909090909091" customWidth="1"/>
+    <col min="11" max="11" width="9.09090909090909" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1" spans="1:12">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="4" t="s">
-        <v>140</v>
+        <v>73</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="I1" s="6" t="str">
-        <f>首页及工序页!N2</f>
-        <v>E53234023200-01</v>
+        <v>74</v>
+      </c>
+      <c r="I1" s="6" t="e">
+        <f>首页及工序页!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="8" t="str">
-        <f>首页及工序页!Q2</f>
-        <v>A4</v>
+        <v>6</v>
+      </c>
+      <c r="K1" s="8" t="e">
+        <f>首页及工序页!#REF!</f>
+        <v>#REF!</v>
       </c>
       <c r="L1" s="9"/>
     </row>
@@ -8959,7 +6599,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
       <c r="G2" s="4" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="H2" s="10"/>
       <c r="I2" s="10"/>
@@ -8969,7 +6609,7 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="37.5" customHeight="1" spans="1:12">
       <c r="A3" s="12" t="s">
-        <v>162</v>
+        <v>94</v>
       </c>
       <c r="B3" s="12"/>
       <c r="C3" s="12"/>
@@ -8983,23 +6623,23 @@
       <c r="K3" s="12"/>
       <c r="L3" s="14"/>
     </row>
-    <row r="4" s="1" customFormat="1" ht="24.75" spans="1:12">
+    <row r="4" s="1" customFormat="1" ht="26" spans="1:12">
       <c r="A4" s="15" t="s">
-        <v>163</v>
+        <v>95</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>164</v>
+        <v>96</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="16" t="s">
-        <v>165</v>
+        <v>97</v>
       </c>
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
       <c r="I4" s="15" t="s">
-        <v>166</v>
+        <v>98</v>
       </c>
       <c r="J4" s="17"/>
       <c r="K4" s="15"/>
@@ -9007,21 +6647,21 @@
     </row>
     <row r="5" s="1" customFormat="1" ht="30.75" customHeight="1" spans="1:12">
       <c r="A5" s="18" t="s">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>168</v>
+        <v>100</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
-      <c r="F5" s="19" t="s">
-        <v>150</v>
+      <c r="F5" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="G5" s="16"/>
       <c r="H5" s="16"/>
       <c r="I5" s="15" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="J5" s="17"/>
       <c r="K5" s="15"/>
@@ -9029,21 +6669,21 @@
     </row>
     <row r="6" s="1" customFormat="1" ht="30.75" customHeight="1" spans="1:12">
       <c r="A6" s="18" t="s">
-        <v>169</v>
+        <v>101</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
-      <c r="F6" s="19" t="s">
-        <v>170</v>
+      <c r="F6" s="16" t="s">
+        <v>102</v>
       </c>
       <c r="G6" s="16"/>
       <c r="H6" s="16"/>
       <c r="I6" s="15" t="s">
-        <v>171</v>
+        <v>103</v>
       </c>
       <c r="J6" s="17"/>
       <c r="K6" s="15"/>
@@ -9051,21 +6691,21 @@
     </row>
     <row r="7" s="1" customFormat="1" ht="30.75" customHeight="1" spans="1:12">
       <c r="A7" s="18" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
-      <c r="F7" s="19" t="s">
-        <v>174</v>
+      <c r="F7" s="16" t="s">
+        <v>106</v>
       </c>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
       <c r="I7" s="15" t="s">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="J7" s="17"/>
       <c r="K7" s="15"/>
@@ -9073,21 +6713,21 @@
     </row>
     <row r="8" s="1" customFormat="1" ht="30.75" customHeight="1" spans="1:12">
       <c r="A8" s="18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="19" t="s">
-        <v>177</v>
+      <c r="F8" s="16" t="s">
+        <v>109</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="16"/>
       <c r="I8" s="15" t="s">
-        <v>175</v>
+        <v>107</v>
       </c>
       <c r="J8" s="17"/>
       <c r="K8" s="15"/>
